--- a/Locators/MobileLocators.xlsx
+++ b/Locators/MobileLocators.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arunk\OneDrive\Desktop\Cucumber\SeleniumCucumber\Locators\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{515811B1-CE47-466B-837B-2168CB7A55A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4072A3B-0A9F-4A18-9BA0-C53EBFE5D0D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="71">
   <si>
     <t>LocatorName</t>
   </si>
@@ -215,6 +215,30 @@
   </si>
   <si>
     <t>//b[contains(text(),"Account Deleted")]</t>
+  </si>
+  <si>
+    <t>Login Email field</t>
+  </si>
+  <si>
+    <t>//input[@data-qa="login-email"]</t>
+  </si>
+  <si>
+    <t>//input[@data-qa="login-password"]</t>
+  </si>
+  <si>
+    <t>Login Password</t>
+  </si>
+  <si>
+    <t>//button[contains(text(),"Login")]</t>
+  </si>
+  <si>
+    <t>Login Button</t>
+  </si>
+  <si>
+    <t>//h2[contains(text(),"Login to your account")]</t>
+  </si>
+  <si>
+    <t>Log into your Account text</t>
   </si>
 </sst>
 </file>
@@ -1571,14 +1595,14 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="41" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1586,7 +1610,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -1594,7 +1618,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -1602,7 +1626,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
@@ -1610,7 +1634,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -1793,6 +1817,38 @@
       </c>
       <c r="B27" s="6" t="s">
         <v>62</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B28" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B29" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B30" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B31" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
